--- a/Figures/Heatmaps/G-heatmap.xlsx
+++ b/Figures/Heatmaps/G-heatmap.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">MIS 12</t>
   </si>
   <si>
-    <t xml:space="preserve">MIS 14</t>
+    <t xml:space="preserve">MIS 13b-14</t>
   </si>
   <si>
     <t xml:space="preserve">MIS 15b</t>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">MIS 20</t>
   </si>
   <si>
-    <t xml:space="preserve">MIS 22</t>
+    <t xml:space="preserve">MIS 22-24</t>
   </si>
   <si>
     <t xml:space="preserve">MIS 26</t>
@@ -220,16 +220,10 @@
     <t xml:space="preserve">Tropical stack</t>
   </si>
   <si>
-    <t xml:space="preserve">Herbert et al. (2010)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ΔMOT (°C)</t>
-  </si>
-  <si>
-    <t>ΔMOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark et al. (2025)</t>
+    <t xml:space="preserve">SST (°C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbert et al. (2017)</t>
   </si>
   <si>
     <t xml:space="preserve">Terrestrial archives</t>
@@ -272,6 +266,12 @@
   </si>
   <si>
     <t xml:space="preserve">Zhao et al. (2021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heqing Basin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wang et al. (2025)</t>
   </si>
   <si>
     <t xml:space="preserve">AP (%) (excl. Gramineae and aquatic/semi-aquatic taxa)</t>
@@ -1234,62 +1234,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3C5485"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA4AFC6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF435B8A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4D6390"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2D8E3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8393B2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AA7C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F4F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF274278"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF395284"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4B628F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4F6591"/>
+        <fgColor rgb="FF5F739B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF385183"/>
       </patternFill>
     </fill>
     <fill>
@@ -1299,17 +1249,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBFC7D7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F3F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4F5F8"/>
+        <fgColor rgb="FFB9C2D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7A8BAC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60749C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF425A89"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF092866"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9B4C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE0E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F8FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1335,6 +1310,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBFC7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC0C8D8"/>
       </patternFill>
     </fill>
@@ -1345,11 +1330,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF60749C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF5A6F98"/>
       </patternFill>
     </fill>
@@ -1380,6 +1360,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD2D8E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF405888"/>
       </patternFill>
     </fill>
@@ -1410,17 +1395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBE0E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF17346E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF425A89"/>
+        <fgColor rgb="FF7687AA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1430,22 +1405,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF14316C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF042362"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E3A73"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF586D97"/>
+        <fgColor rgb="FF3C5485"/>
       </patternFill>
     </fill>
     <fill>
@@ -1456,6 +1416,46 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF9FABC3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF14316C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF274278"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF042362"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E3A73"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4B628F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF395284"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF586D97"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF2B467B"/>
       </patternFill>
     </fill>
@@ -1466,6 +1466,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF4D6390"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF0E2C69"/>
       </patternFill>
     </fill>
@@ -1481,11 +1486,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF385183"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF354E81"/>
       </patternFill>
     </fill>
@@ -1496,11 +1496,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7A8BAC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF798AAB"/>
       </patternFill>
     </fill>
@@ -1511,11 +1506,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7687AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF8493B2"/>
       </patternFill>
     </fill>
@@ -1526,16 +1516,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF4F6591"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF435B8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF2D477C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3D5586"/>
+        <fgColor rgb="FF17346E"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="25">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -1558,9 +1558,7 @@
         <color theme="1"/>
       </right>
       <top style="none"/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -1573,9 +1571,7 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -1610,10 +1606,8 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
+      <right style="none"/>
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="none"/>
@@ -1621,16 +1615,16 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="1"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color theme="1"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color theme="1"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -1653,11 +1647,35 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
+      <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -1668,9 +1686,7 @@
         <color theme="1"/>
       </right>
       <top style="none"/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -1722,6 +1738,17 @@
         <color theme="1"/>
       </right>
       <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -1732,6 +1759,21 @@
     <border>
       <left style="thin">
         <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
       </left>
       <right style="thin">
         <color theme="1"/>
@@ -1815,12 +1857,12 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="288">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" quotePrefix="0" pivotButton="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
       <protection locked="1"/>
     </xf>
@@ -1845,300 +1887,840 @@
     <xf fontId="3" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="4" fillId="3" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="4" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="5" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="6" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="7" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="8" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="9" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="10" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="11" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="12" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="13" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="14" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="15" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="16" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="17" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="18" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="19" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="20" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="21" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="22" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="23" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="24" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="25" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="4" fillId="3" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="5" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="6" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="8" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="9" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="10" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="11" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="12" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="13" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="14" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="15" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="16" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="17" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="18" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="19" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="20" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="21" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="22" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="23" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="24" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="25" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="2" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="26" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="27" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="28" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="29" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="30" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="31" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="32" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="33" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="34" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="35" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="36" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="37" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="38" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="39" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="40" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="41" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="42" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="43" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="44" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="45" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="46" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="47" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="48" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="49" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="50" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="51" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="52" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="53" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="54" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="55" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="56" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="57" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="58" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="59" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="60" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="61" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="62" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="63" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="64" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="65" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="66" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="67" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="68" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="69" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="70" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="71" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="72" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="73" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="74" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="75" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="76" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="77" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="78" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="79" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="80" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="81" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="82" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="83" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="84" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="85" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="86" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="87" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="88" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="89" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="90" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="91" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="92" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="93" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="94" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="95" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="96" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="97" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="98" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="99" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="100" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="101" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="102" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="103" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="104" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="105" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="4" fillId="26" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="27" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="28" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="29" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="30" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="31" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="32" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="33" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="34" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="35" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="36" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="37" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="38" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="39" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="40" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="41" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="42" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="43" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="44" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="45" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="46" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="47" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="48" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="49" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="50" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="51" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="52" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="53" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="54" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="55" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="56" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="57" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="58" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="59" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="60" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="61" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="62" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="63" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="64" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="65" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="66" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="67" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="68" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="69" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="70" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="71" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="72" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="73" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="74" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="75" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="76" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="77" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="78" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="79" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="80" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="2" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf fontId="4" fillId="81" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="82" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="83" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="84" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="85" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="86" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="87" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="88" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="89" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="90" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="91" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="92" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="93" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="94" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="95" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="96" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="97" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="98" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="99" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="100" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="101" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="102" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="103" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="104" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="105" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="106" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="107" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="108" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="109" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="110" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="111" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="112" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="113" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="114" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="115" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="116" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="117" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="118" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="119" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="120" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="121" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="122" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="123" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="124" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="125" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="126" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="127" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="128" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="129" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="130" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="131" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="132" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="133" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="134" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="135" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="136" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="137" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="138" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="139" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="140" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="141" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="142" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="143" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="144" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="145" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="146" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="147" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="148" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="149" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="150" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="151" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="152" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="153" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="154" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="155" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="156" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="157" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="158" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="159" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="160" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="161" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="162" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="163" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="164" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="165" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="166" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="167" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="168" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="169" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="170" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="171" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="172" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="173" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="174" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="175" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="176" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="177" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="178" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="179" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="180" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="181" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="182" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="183" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="2" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center" textRotation="90" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf fontId="4" fillId="184" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="185" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="186" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="187" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="188" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="189" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="190" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="191" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="1" fillId="192" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="106" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="107" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="108" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="109" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="110" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="111" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="112" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="113" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="114" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="115" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="116" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="117" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="118" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="119" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="120" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="121" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="122" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="123" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="124" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="125" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="126" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="127" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="128" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="129" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="130" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="131" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="132" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="133" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="134" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="135" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="136" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="137" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="138" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="139" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="140" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="141" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="142" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="143" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="144" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="145" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="146" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="147" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="148" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="149" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="150" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="151" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="152" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="153" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="154" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="155" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="156" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="157" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="158" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="159" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="160" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="161" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="162" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="163" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="164" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="165" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="166" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="167" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="168" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="169" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="170" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="171" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="172" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="173" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="174" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="175" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="193" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="194" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="195" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="192" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="8" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="176" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="95" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="177" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="178" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="32" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="179" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="180" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="181" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="182" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="183" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="184" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="59" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="35" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="77" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="125" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="166" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="121" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="185" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="75" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="164" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="22" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="186" borderId="17" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="187" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="196" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="197" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="2" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="198" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="199" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="200" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="201" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="202" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="203" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="204" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="2" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="3" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="4" fillId="188" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="189" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="190" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="191" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="192" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="187" borderId="20" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" textRotation="90" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="205" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="206" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="207" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="208" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="209" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="210" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="211" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="212" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="213" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="214" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="215" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="216" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="217" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="218" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="3" fillId="193" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="194" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="181" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="195" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="196" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="197" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="198" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="199" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="200" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="201" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="202" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="203" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="204" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="205" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="206" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="207" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="185" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="208" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="184" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="182" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="209" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="210" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="211" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="179" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="212" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="213" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="214" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="215" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="216" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="217" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="218" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="4" fillId="219" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="220" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="221" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="222" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="223" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="224" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="225" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="226" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="227" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="228" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="229" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="230" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="231" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="232" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="233" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="234" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="192" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="220" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="221" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="222" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="223" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="178" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="224" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="225" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="177" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="226" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="227" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="180" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="228" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="229" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="230" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="231" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="232" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="233" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="234" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="187" borderId="14" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="2" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="235" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="4" fillId="235" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2667,6 +3249,8 @@
     <col customWidth="1" min="2" max="2" width="52.421875"/>
     <col customWidth="1" min="3" max="3" width="23.00390625"/>
     <col customWidth="1" min="4" max="4" width="35.140625"/>
+    <col customWidth="1" min="11" max="11" width="11.140625"/>
+    <col customWidth="1" min="16" max="16" width="10.421875"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3169,70 +3753,70 @@
     </row>
     <row r="7">
       <c r="A7" s="33"/>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="108" t="s">
+      <c r="C7" s="109" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="110" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="109">
+      <c r="E7" s="111">
         <v>-3.29</v>
       </c>
       <c r="F7" s="58">
         <v>-3.0699999999999998</v>
       </c>
-      <c r="G7" s="110">
+      <c r="G7" s="112">
         <v>-1.8500000000000001</v>
       </c>
-      <c r="H7" s="111">
+      <c r="H7" s="113">
         <v>-3.0499999999999998</v>
       </c>
       <c r="I7" s="37">
         <v>-3.1200000000000001</v>
       </c>
-      <c r="J7" s="112">
+      <c r="J7" s="114">
         <v>-3.8300000000000001</v>
       </c>
       <c r="K7" s="38">
         <v>-3.02</v>
       </c>
-      <c r="L7" s="113">
+      <c r="L7" s="115">
         <v>-1.4099999999999999</v>
       </c>
-      <c r="M7" s="114">
+      <c r="M7" s="116">
         <v>-2.79</v>
       </c>
-      <c r="N7" s="115">
+      <c r="N7" s="117">
         <v>-2.7200000000000002</v>
       </c>
       <c r="O7" s="15">
         <v>-3.8700000000000001</v>
       </c>
-      <c r="P7" s="116">
+      <c r="P7" s="118">
         <v>-3.5800000000000001</v>
       </c>
       <c r="Q7" s="64">
         <v>-1.73</v>
       </c>
-      <c r="R7" s="117">
+      <c r="R7" s="119">
         <v>-1.8700000000000001</v>
       </c>
-      <c r="S7" s="118">
+      <c r="S7" s="120">
         <v>-1.6100000000000001</v>
       </c>
       <c r="T7" s="12">
         <v>-1.3500000000000001</v>
       </c>
-      <c r="U7" s="119">
+      <c r="U7" s="121">
         <v>-1.8300000000000001</v>
       </c>
       <c r="V7" s="52">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="W7" s="110">
+      <c r="W7" s="112">
         <v>-1.8600000000000001</v>
       </c>
       <c r="X7" s="71">
@@ -3241,7 +3825,7 @@
       <c r="Y7" s="30">
         <v>-0.65000000000000002</v>
       </c>
-      <c r="Z7" s="120">
+      <c r="Z7" s="122">
         <v>-0.94999999999999996</v>
       </c>
       <c r="AA7" s="29">
@@ -3253,29 +3837,29 @@
     </row>
     <row r="8">
       <c r="A8" s="33"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="108"/>
+      <c r="C8" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="121">
+      <c r="E8" s="125">
         <v>-5.8099999999999996</v>
       </c>
-      <c r="F8" s="122">
+      <c r="F8" s="126">
         <v>-5.21</v>
       </c>
-      <c r="G8" s="123">
+      <c r="G8" s="127">
         <v>-3.6000000000000001</v>
       </c>
       <c r="H8" s="13">
         <v>-4.7300000000000004</v>
       </c>
-      <c r="I8" s="124">
+      <c r="I8" s="128">
         <v>-6.46</v>
       </c>
-      <c r="J8" s="125">
+      <c r="J8" s="129">
         <v>-6.8799999999999999</v>
       </c>
       <c r="K8" s="96">
@@ -3284,7 +3868,7 @@
       <c r="L8" s="29">
         <v>-1.95</v>
       </c>
-      <c r="M8" s="126">
+      <c r="M8" s="130">
         <v>-4.3899999999999997</v>
       </c>
       <c r="N8" s="41">
@@ -3293,19 +3877,19 @@
       <c r="O8" s="15">
         <v>-7.5899999999999999</v>
       </c>
-      <c r="P8" s="126">
+      <c r="P8" s="130">
         <v>-4.3899999999999997</v>
       </c>
       <c r="Q8" s="26">
         <v>-3.48</v>
       </c>
-      <c r="R8" s="127">
+      <c r="R8" s="131">
         <v>-5.3700000000000001</v>
       </c>
-      <c r="S8" s="128">
+      <c r="S8" s="132">
         <v>-3.71</v>
       </c>
-      <c r="T8" s="129">
+      <c r="T8" s="133">
         <v>-3.7599999999999998</v>
       </c>
       <c r="U8" s="51">
@@ -3314,7 +3898,7 @@
       <c r="V8" s="22">
         <v>-2.52</v>
       </c>
-      <c r="W8" s="130">
+      <c r="W8" s="134">
         <v>-4.6299999999999999</v>
       </c>
       <c r="X8" s="53">
@@ -3335,68 +3919,68 @@
     </row>
     <row r="9">
       <c r="A9" s="33"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="108"/>
+      <c r="C9" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="131">
+      <c r="E9" s="135">
         <v>-3.2000000000000002</v>
       </c>
-      <c r="F9" s="132">
+      <c r="F9" s="136">
         <v>-1.9199999999999999</v>
       </c>
       <c r="G9" s="25">
         <v>-1.3600000000000001</v>
       </c>
-      <c r="H9" s="133">
+      <c r="H9" s="137">
         <v>-2.73</v>
       </c>
-      <c r="I9" s="134">
+      <c r="I9" s="138">
         <v>-3.04</v>
       </c>
       <c r="J9" s="15">
         <v>-5.2000000000000002</v>
       </c>
-      <c r="K9" s="135">
+      <c r="K9" s="139">
         <v>-4.3399999999999999</v>
       </c>
-      <c r="L9" s="136">
+      <c r="L9" s="140">
         <v>-1.9099999999999999</v>
       </c>
-      <c r="M9" s="137">
+      <c r="M9" s="141">
         <v>-4.25</v>
       </c>
       <c r="N9" s="97">
         <v>-3.1699999999999999</v>
       </c>
-      <c r="O9" s="138">
+      <c r="O9" s="142">
         <v>-4.1299999999999999</v>
       </c>
-      <c r="P9" s="139">
+      <c r="P9" s="143">
         <v>-4.3200000000000003</v>
       </c>
-      <c r="Q9" s="140">
+      <c r="Q9" s="144">
         <v>-2.23</v>
       </c>
-      <c r="R9" s="141">
+      <c r="R9" s="145">
         <v>-2.4199999999999999</v>
       </c>
-      <c r="S9" s="142">
+      <c r="S9" s="146">
         <v>-2.8999999999999999</v>
       </c>
-      <c r="T9" s="143">
+      <c r="T9" s="147">
         <v>-0.63</v>
       </c>
-      <c r="U9" s="144">
+      <c r="U9" s="148">
         <v>-1.8700000000000001</v>
       </c>
-      <c r="V9" s="110">
+      <c r="V9" s="112">
         <v>-1.79</v>
       </c>
-      <c r="W9" s="145">
+      <c r="W9" s="149">
         <v>-2.2999999999999998</v>
       </c>
       <c r="X9" s="29">
@@ -3405,10 +3989,10 @@
       <c r="Y9" s="29">
         <v>0.71999999999999997</v>
       </c>
-      <c r="Z9" s="146">
+      <c r="Z9" s="150">
         <v>-0.47999999999999998</v>
       </c>
-      <c r="AA9" s="147">
+      <c r="AA9" s="151">
         <v>0.65000000000000002</v>
       </c>
       <c r="AB9" s="59">
@@ -3417,26 +4001,26 @@
     </row>
     <row r="10">
       <c r="A10" s="33"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="35" t="s">
+      <c r="B10" s="108"/>
+      <c r="C10" s="123" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="115">
+      <c r="E10" s="117">
         <v>-3.8500000000000001</v>
       </c>
-      <c r="F10" s="148">
+      <c r="F10" s="152">
         <v>-3.75</v>
       </c>
       <c r="G10" s="64">
         <v>-2.3300000000000001</v>
       </c>
-      <c r="H10" s="149">
+      <c r="H10" s="153">
         <v>-4.2599999999999998</v>
       </c>
-      <c r="I10" s="142">
+      <c r="I10" s="146">
         <v>-3.5299999999999998</v>
       </c>
       <c r="J10" s="95">
@@ -3448,80 +4032,80 @@
       <c r="L10" s="67">
         <v>-2.3100000000000001</v>
       </c>
-      <c r="M10" s="150">
+      <c r="M10" s="154">
         <v>-4.46</v>
       </c>
-      <c r="N10" s="131">
+      <c r="N10" s="135">
         <v>-3.7999999999999998</v>
       </c>
-      <c r="O10" s="151">
+      <c r="O10" s="155">
         <v>-4.0599999999999996</v>
       </c>
-      <c r="P10" s="131">
+      <c r="P10" s="135">
         <v>-3.7999999999999998</v>
       </c>
-      <c r="Q10" s="152">
+      <c r="Q10" s="156">
         <v>-3.6800000000000002</v>
       </c>
-      <c r="R10" s="153">
+      <c r="R10" s="157">
         <v>-2.6899999999999999</v>
       </c>
-      <c r="S10" s="154">
+      <c r="S10" s="158">
         <v>-3.4399999999999999</v>
       </c>
-      <c r="T10" s="151">
+      <c r="T10" s="155">
         <v>-4.0700000000000003</v>
       </c>
       <c r="U10" s="15">
         <v>-5.6399999999999997</v>
       </c>
-      <c r="V10" s="150">
+      <c r="V10" s="154">
         <v>-4.4699999999999998</v>
       </c>
-      <c r="W10" s="114">
+      <c r="W10" s="116">
         <v>-3.98</v>
       </c>
-      <c r="X10" s="155">
+      <c r="X10" s="159">
         <v>-3.71</v>
       </c>
       <c r="Y10" s="29">
         <v>-0.22</v>
       </c>
-      <c r="Z10" s="156">
+      <c r="Z10" s="160">
         <v>-0.96999999999999997</v>
       </c>
-      <c r="AA10" s="123">
+      <c r="AA10" s="127">
         <v>-1.79</v>
       </c>
-      <c r="AB10" s="157">
+      <c r="AB10" s="161">
         <v>-1.6399999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="33"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35" t="s">
+      <c r="B11" s="108"/>
+      <c r="C11" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="158">
+      <c r="E11" s="162">
         <v>-2.6499999999999999</v>
       </c>
-      <c r="F11" s="116">
+      <c r="F11" s="118">
         <v>-3.4399999999999999</v>
       </c>
-      <c r="G11" s="159">
+      <c r="G11" s="163">
         <v>-1.29</v>
       </c>
-      <c r="H11" s="114">
+      <c r="H11" s="116">
         <v>-2.3799999999999999</v>
       </c>
-      <c r="I11" s="134">
+      <c r="I11" s="138">
         <v>-2.1000000000000001</v>
       </c>
-      <c r="J11" s="160">
+      <c r="J11" s="164">
         <v>-3.4199999999999999</v>
       </c>
       <c r="K11" s="15">
@@ -3530,19 +4114,19 @@
       <c r="L11" s="73">
         <v>-0.56999999999999995</v>
       </c>
-      <c r="M11" s="161">
+      <c r="M11" s="165">
         <v>-2.4900000000000002</v>
       </c>
-      <c r="N11" s="162">
+      <c r="N11" s="166">
         <v>-1.6100000000000001</v>
       </c>
       <c r="O11" s="15">
         <v>-3.8300000000000001</v>
       </c>
-      <c r="P11" s="163">
+      <c r="P11" s="167">
         <v>-3.6400000000000001</v>
       </c>
-      <c r="Q11" s="164">
+      <c r="Q11" s="168">
         <v>-0.79000000000000004</v>
       </c>
       <c r="R11" s="68">
@@ -3554,16 +4138,16 @@
       <c r="T11" s="44">
         <v>-1.3100000000000001</v>
       </c>
-      <c r="U11" s="159">
+      <c r="U11" s="163">
         <v>-1.3</v>
       </c>
       <c r="V11" s="104">
         <v>-0.67000000000000004</v>
       </c>
-      <c r="W11" s="128">
+      <c r="W11" s="132">
         <v>-0.55000000000000004</v>
       </c>
-      <c r="X11" s="136">
+      <c r="X11" s="140">
         <v>-1.1799999999999999</v>
       </c>
       <c r="Y11" s="29">
@@ -3572,35 +4156,35 @@
       <c r="Z11" s="87">
         <v>-0.82999999999999996</v>
       </c>
-      <c r="AA11" s="165">
+      <c r="AA11" s="169">
         <v>0.89000000000000001</v>
       </c>
-      <c r="AB11" s="166">
+      <c r="AB11" s="170">
         <v>0.40999999999999998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="33"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35" t="s">
+      <c r="B12" s="108"/>
+      <c r="C12" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="167">
+      <c r="E12" s="171">
         <v>-2.3900000000000001</v>
       </c>
-      <c r="F12" s="149">
+      <c r="F12" s="153">
         <v>-1.8799999999999999</v>
       </c>
-      <c r="G12" s="159">
+      <c r="G12" s="163">
         <v>-1.28</v>
       </c>
       <c r="H12" s="75">
         <v>-2.0299999999999998</v>
       </c>
-      <c r="I12" s="163">
+      <c r="I12" s="167">
         <v>-2.3500000000000001</v>
       </c>
       <c r="J12" s="15">
@@ -3609,10 +4193,10 @@
       <c r="K12" s="96">
         <v>-1.01</v>
       </c>
-      <c r="L12" s="156">
+      <c r="L12" s="160">
         <v>-0.56000000000000005</v>
       </c>
-      <c r="M12" s="153">
+      <c r="M12" s="157">
         <v>-1.25</v>
       </c>
       <c r="N12" s="77">
@@ -3630,16 +4214,16 @@
       <c r="R12" s="76">
         <v>-1.24</v>
       </c>
-      <c r="S12" s="144">
+      <c r="S12" s="148">
         <v>-1.21</v>
       </c>
       <c r="T12" s="70">
         <v>-0.81999999999999995</v>
       </c>
-      <c r="U12" s="117">
+      <c r="U12" s="119">
         <v>-1.1899999999999999</v>
       </c>
-      <c r="V12" s="168">
+      <c r="V12" s="172">
         <v>-0.70999999999999996</v>
       </c>
       <c r="W12" s="64">
@@ -3651,26 +4235,26 @@
       <c r="Y12" s="48">
         <v>-0.78000000000000003</v>
       </c>
-      <c r="Z12" s="169">
+      <c r="Z12" s="173">
         <v>-0.93000000000000005</v>
       </c>
       <c r="AA12" s="29">
         <v>-0.26000000000000001</v>
       </c>
-      <c r="AB12" s="170">
+      <c r="AB12" s="174">
         <v>-0.40999999999999998</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="35" t="s">
+      <c r="B13" s="108"/>
+      <c r="C13" s="123" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="171">
+      <c r="E13" s="175">
         <v>-3.8900000000000001</v>
       </c>
       <c r="F13" s="20">
@@ -3679,46 +4263,46 @@
       <c r="G13" s="27">
         <v>-2.1499999999999999</v>
       </c>
-      <c r="H13" s="171">
+      <c r="H13" s="175">
         <v>-3.8799999999999999</v>
       </c>
-      <c r="I13" s="172">
+      <c r="I13" s="176">
         <v>-3.9300000000000002</v>
       </c>
-      <c r="J13" s="173">
+      <c r="J13" s="177">
         <v>-4.6299999999999999</v>
       </c>
       <c r="K13" s="83">
         <v>-3.8100000000000001</v>
       </c>
-      <c r="L13" s="174">
+      <c r="L13" s="178">
         <v>-1.4299999999999999</v>
       </c>
       <c r="M13" s="15">
         <v>-5.8499999999999996</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="149">
         <v>-3.6200000000000001</v>
       </c>
-      <c r="O13" s="135">
+      <c r="O13" s="139">
         <v>-5.1799999999999997</v>
       </c>
-      <c r="P13" s="175">
+      <c r="P13" s="179">
         <v>-4.9699999999999998</v>
       </c>
-      <c r="Q13" s="176">
+      <c r="Q13" s="180">
         <v>-2.5099999999999998</v>
       </c>
-      <c r="R13" s="177">
+      <c r="R13" s="181">
         <v>-2.48</v>
       </c>
       <c r="S13" s="44">
         <v>-3.4300000000000002</v>
       </c>
-      <c r="T13" s="178">
+      <c r="T13" s="182">
         <v>-2.79</v>
       </c>
-      <c r="U13" s="179">
+      <c r="U13" s="183">
         <v>-2.8399999999999999</v>
       </c>
       <c r="V13" s="72">
@@ -3727,77 +4311,77 @@
       <c r="W13" s="27">
         <v>-2.1600000000000001</v>
       </c>
-      <c r="X13" s="180">
+      <c r="X13" s="184">
         <v>-2.1800000000000002</v>
       </c>
-      <c r="Y13" s="181">
+      <c r="Y13" s="185">
         <v>-2.7400000000000002</v>
       </c>
-      <c r="Z13" s="157">
+      <c r="Z13" s="161">
         <v>-2.4900000000000002</v>
       </c>
       <c r="AA13" s="29">
         <v>-1.29</v>
       </c>
-      <c r="AB13" s="182">
+      <c r="AB13" s="186">
         <v>-1.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="35" t="s">
+      <c r="B14" s="108"/>
+      <c r="C14" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="124" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="42">
         <v>-2.4199999999999999</v>
       </c>
-      <c r="F14" s="183">
+      <c r="F14" s="187">
         <v>-1.74</v>
       </c>
       <c r="G14" s="13">
         <v>-1.1100000000000001</v>
       </c>
-      <c r="H14" s="184">
+      <c r="H14" s="188">
         <v>-2.0600000000000001</v>
       </c>
-      <c r="I14" s="185">
+      <c r="I14" s="189">
         <v>-2.1899999999999999</v>
       </c>
       <c r="J14" s="15">
         <v>-2.5600000000000001</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="166">
         <v>-1.22</v>
       </c>
       <c r="L14" s="31">
         <v>-0.38</v>
       </c>
-      <c r="M14" s="145">
+      <c r="M14" s="149">
         <v>-1.1599999999999999</v>
       </c>
-      <c r="N14" s="142">
+      <c r="N14" s="146">
         <v>-1.45</v>
       </c>
-      <c r="O14" s="186">
+      <c r="O14" s="190">
         <v>-1.97</v>
       </c>
       <c r="P14" s="74">
         <v>-2.0299999999999998</v>
       </c>
-      <c r="Q14" s="113">
+      <c r="Q14" s="115">
         <v>-0.55000000000000004</v>
       </c>
       <c r="R14" s="67">
         <v>-0.80000000000000004</v>
       </c>
-      <c r="S14" s="187">
+      <c r="S14" s="191">
         <v>-0.88</v>
       </c>
-      <c r="T14" s="188">
+      <c r="T14" s="192">
         <v>-0.19</v>
       </c>
       <c r="U14" s="51">
@@ -3812,795 +4396,789 @@
       <c r="X14" s="17">
         <v>-0.14999999999999999</v>
       </c>
-      <c r="Y14" s="189">
+      <c r="Y14" s="193">
         <v>-0.14000000000000001</v>
       </c>
-      <c r="Z14" s="113">
+      <c r="Z14" s="115">
         <v>-0.56000000000000005</v>
       </c>
       <c r="AA14" s="29">
         <v>0.29999999999999999</v>
       </c>
-      <c r="AB14" s="190">
+      <c r="AB14" s="194">
         <v>-0.13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="93" t="s">
+      <c r="A15" s="195"/>
+      <c r="B15" s="196" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="197" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="94" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="191">
-        <v>-1.6020000000000001</v>
-      </c>
-      <c r="F15" s="192">
-        <v>-0.63800000000000001</v>
-      </c>
-      <c r="G15" s="156">
-        <v>-0.108</v>
-      </c>
-      <c r="H15" s="133">
-        <v>-1.1759999999999999</v>
-      </c>
-      <c r="I15" s="193">
-        <v>-1.54</v>
-      </c>
-      <c r="J15" s="175">
-        <v>-1.7050000000000001</v>
-      </c>
-      <c r="K15" s="179">
-        <v>-0.60099999999999998</v>
-      </c>
-      <c r="L15" s="98">
-        <v>0.045999999999999999</v>
-      </c>
-      <c r="M15" s="88">
-        <v>-0.68999999999999995</v>
-      </c>
-      <c r="N15" s="82">
-        <v>-1.0680000000000001</v>
-      </c>
-      <c r="O15" s="194">
-        <v>-1.4450000000000001</v>
-      </c>
-      <c r="P15" s="15">
-        <v>-2.1669999999999998</v>
-      </c>
-      <c r="Q15" s="157">
-        <v>-0.40799999999999997</v>
-      </c>
-      <c r="R15" s="195">
-        <v>-0.20499999999999999</v>
-      </c>
-      <c r="S15" s="46">
-        <v>-1.1100000000000001</v>
-      </c>
-      <c r="T15" s="118">
-        <v>-0.628</v>
-      </c>
-      <c r="U15" s="145">
-        <v>-0.996</v>
-      </c>
-      <c r="V15" s="181">
-        <v>-0.53800000000000003</v>
-      </c>
-      <c r="W15" s="196">
-        <v>-0.93799999999999994</v>
-      </c>
-      <c r="X15" s="32">
-        <v>-0.10000000000000001</v>
-      </c>
-      <c r="Y15" s="73">
-        <v>-0.53500000000000003</v>
-      </c>
-      <c r="Z15" s="197">
-        <v>-0.73099999999999998</v>
-      </c>
-      <c r="AA15" s="29">
-        <v>0.219</v>
-      </c>
-      <c r="AB15" s="198">
-        <v>0.094</v>
+      <c r="D15" s="198" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="199">
+        <v>23.943999999999999</v>
+      </c>
+      <c r="F15" s="200">
+        <v>25.009</v>
+      </c>
+      <c r="G15" s="201">
+        <v>25.593</v>
+      </c>
+      <c r="H15" s="202">
+        <v>24.571999999999999</v>
+      </c>
+      <c r="I15" s="203">
+        <v>24.262</v>
+      </c>
+      <c r="J15" s="204">
+        <v>24.158000000000001</v>
+      </c>
+      <c r="K15" s="205">
+        <v>25.337</v>
+      </c>
+      <c r="L15" s="206">
+        <v>26.015000000000001</v>
+      </c>
+      <c r="M15" s="207">
+        <v>25.314</v>
+      </c>
+      <c r="N15" s="208">
+        <v>25.027000000000001</v>
+      </c>
+      <c r="O15" s="209">
+        <v>24.684000000000001</v>
+      </c>
+      <c r="P15" s="210">
+        <v>24.050999999999998</v>
+      </c>
+      <c r="Q15" s="211">
+        <v>25.844000000000001</v>
+      </c>
+      <c r="R15" s="212">
+        <v>26.081</v>
+      </c>
+      <c r="S15" s="213">
+        <v>25.212</v>
+      </c>
+      <c r="T15" s="214">
+        <v>25.722999999999999</v>
+      </c>
+      <c r="U15" s="215">
+        <v>25.378</v>
+      </c>
+      <c r="V15" s="216">
+        <v>25.893999999999998</v>
+      </c>
+      <c r="W15" s="217">
+        <v>25.539000000000001</v>
+      </c>
+      <c r="X15" s="218">
+        <v>26.402000000000001</v>
+      </c>
+      <c r="Y15" s="219">
+        <v>25.998000000000001</v>
+      </c>
+      <c r="Z15" s="220">
+        <v>25.834</v>
+      </c>
+      <c r="AA15" s="221">
+        <v>26.809000000000001</v>
+      </c>
+      <c r="AB15" s="222">
+        <v>26.716999999999999</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="199"/>
-      <c r="B16" s="200" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="201" t="s">
+      <c r="A16" s="223" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="202" t="s">
+      <c r="B16" s="224" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="203">
-        <v>-3.4300000000000002</v>
-      </c>
-      <c r="F16" s="150">
-        <v>-3.2000000000000002</v>
-      </c>
-      <c r="G16" s="153">
-        <v>-1.98</v>
-      </c>
-      <c r="H16" s="204">
-        <v>-3.1800000000000002</v>
-      </c>
-      <c r="I16" s="124">
-        <v>-3.2599999999999998</v>
-      </c>
-      <c r="J16" s="112">
-        <v>-3.9700000000000002</v>
-      </c>
-      <c r="K16" s="111">
-        <v>-3.1499999999999999</v>
-      </c>
-      <c r="L16" s="104">
-        <v>-1.54</v>
-      </c>
-      <c r="M16" s="205">
-        <v>-2.9199999999999999</v>
-      </c>
-      <c r="N16" s="206">
-        <v>-2.8500000000000001</v>
-      </c>
-      <c r="O16" s="15">
-        <v>-4.0099999999999998</v>
-      </c>
-      <c r="P16" s="207">
-        <v>-3.7200000000000002</v>
-      </c>
-      <c r="Q16" s="197">
-        <v>-1.7609171029999999</v>
-      </c>
-      <c r="R16" s="100">
-        <v>-1.86000056</v>
-      </c>
-      <c r="S16" s="178">
-        <v>-1.5268758929999999</v>
-      </c>
-      <c r="T16" s="208">
-        <v>-1.2284010059999999</v>
-      </c>
-      <c r="U16" s="96">
-        <v>-1.5858515369999999</v>
-      </c>
-      <c r="V16" s="120">
-        <v>-0.91398455700000003</v>
-      </c>
-      <c r="W16" s="113">
-        <v>-1.4033357200000001</v>
-      </c>
-      <c r="X16" s="107">
-        <v>-0.74760148999999998</v>
-      </c>
-      <c r="Y16" s="209">
-        <v>-0.50033449200000002</v>
-      </c>
-      <c r="Z16" s="66">
-        <v>-0.65581840300000005</v>
-      </c>
-      <c r="AA16" s="29">
-        <v>-0.29410086400000002</v>
-      </c>
-      <c r="AB16" s="210">
-        <v>-0.45651828100000003</v>
+      <c r="C16" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="225" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="226">
+        <v>-0.086680779999999999</v>
+      </c>
+      <c r="F16" s="165">
+        <v>-0.23880960000000001</v>
+      </c>
+      <c r="G16" s="68">
+        <v>0.074894379999999997</v>
+      </c>
+      <c r="H16" s="168">
+        <v>0.22877310000000001</v>
+      </c>
+      <c r="I16" s="158">
+        <v>-0.077691079999999996</v>
+      </c>
+      <c r="J16" s="134">
+        <v>0.07971615</v>
+      </c>
+      <c r="K16" s="174">
+        <v>0.61690820000000002</v>
+      </c>
+      <c r="L16" s="186">
+        <v>0.64194669999999998</v>
+      </c>
+      <c r="M16" s="43">
+        <v>0.03047743</v>
+      </c>
+      <c r="N16" s="180">
+        <v>0.35141810000000001</v>
+      </c>
+      <c r="O16" s="70">
+        <v>0.3707163</v>
+      </c>
+      <c r="P16" s="153">
+        <v>-0.27278079999999999</v>
+      </c>
+      <c r="Q16" s="22">
+        <v>0.57443069999999996</v>
+      </c>
+      <c r="R16" s="227">
+        <v>0.65269790000000005</v>
+      </c>
+      <c r="S16" s="228">
+        <v>0.67759029999999998</v>
+      </c>
+      <c r="T16" s="29">
+        <v>0.70569550000000003</v>
+      </c>
+      <c r="U16" s="229">
+        <v>0.37361359999999999</v>
+      </c>
+      <c r="V16" s="84">
+        <v>0.44565630000000001</v>
+      </c>
+      <c r="W16" s="15">
+        <v>-0.61156650000000001</v>
+      </c>
+      <c r="X16" s="103">
+        <v>0.42185270000000002</v>
+      </c>
+      <c r="Y16" s="49">
+        <v>0.56740990000000002</v>
+      </c>
+      <c r="Z16" s="186">
+        <v>0.63937180000000005</v>
+      </c>
+      <c r="AA16" s="230">
+        <v>0.63482479999999997</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>0.49958469999999999</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="211" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="212" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="108" t="s">
+      <c r="A17" s="231"/>
+      <c r="B17" s="232" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="C17" s="123" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="213">
-        <v>-0.086680779999999999</v>
-      </c>
-      <c r="F17" s="161">
-        <v>-0.23880960000000001</v>
-      </c>
-      <c r="G17" s="68">
-        <v>0.074894379999999997</v>
-      </c>
-      <c r="H17" s="164">
-        <v>0.22877310000000001</v>
-      </c>
-      <c r="I17" s="154">
-        <v>-0.077691079999999996</v>
+      <c r="D17" s="124" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="145">
+        <v>44.015000000000001</v>
+      </c>
+      <c r="F17" s="18">
+        <v>46.975000000000001</v>
+      </c>
+      <c r="G17" s="121">
+        <v>40.731999999999999</v>
+      </c>
+      <c r="H17" s="181">
+        <v>36.220999999999997</v>
+      </c>
+      <c r="I17" s="166">
+        <v>44.176000000000002</v>
       </c>
       <c r="J17" s="130">
-        <v>0.07971615</v>
-      </c>
-      <c r="K17" s="170">
-        <v>0.61690820000000002</v>
-      </c>
-      <c r="L17" s="182">
-        <v>0.64194669999999998</v>
-      </c>
-      <c r="M17" s="43">
-        <v>0.03047743</v>
-      </c>
-      <c r="N17" s="176">
-        <v>0.35141810000000001</v>
-      </c>
-      <c r="O17" s="70">
-        <v>0.3707163</v>
-      </c>
-      <c r="P17" s="149">
-        <v>-0.27278079999999999</v>
-      </c>
-      <c r="Q17" s="22">
-        <v>0.57443069999999996</v>
-      </c>
-      <c r="R17" s="214">
-        <v>0.65269790000000005</v>
-      </c>
-      <c r="S17" s="215">
-        <v>0.67759029999999998</v>
-      </c>
-      <c r="T17" s="29">
-        <v>0.70569550000000003</v>
-      </c>
-      <c r="U17" s="208">
-        <v>0.37361359999999999</v>
-      </c>
-      <c r="V17" s="84">
-        <v>0.44565630000000001</v>
-      </c>
-      <c r="W17" s="15">
-        <v>-0.61156650000000001</v>
-      </c>
-      <c r="X17" s="103">
-        <v>0.42185270000000002</v>
-      </c>
-      <c r="Y17" s="49">
-        <v>0.56740990000000002</v>
-      </c>
-      <c r="Z17" s="182">
-        <v>0.63937180000000005</v>
-      </c>
-      <c r="AA17" s="198">
-        <v>0.63482479999999997</v>
-      </c>
-      <c r="AB17" s="17">
-        <v>0.49958469999999999</v>
+        <v>41.243000000000002</v>
+      </c>
+      <c r="K17" s="193">
+        <v>33.155999999999999</v>
+      </c>
+      <c r="L17" s="17">
+        <v>33.212000000000003</v>
+      </c>
+      <c r="M17" s="15">
+        <v>57.716000000000001</v>
+      </c>
+      <c r="N17" s="115">
+        <v>37.366</v>
+      </c>
+      <c r="O17" s="233">
+        <v>35.841999999999999</v>
+      </c>
+      <c r="P17" s="111">
+        <v>52.939</v>
+      </c>
+      <c r="Q17" s="85">
+        <v>31.253</v>
+      </c>
+      <c r="R17" s="194">
+        <v>33.040999999999997</v>
+      </c>
+      <c r="S17" s="30">
+        <v>30.943000000000001</v>
+      </c>
+      <c r="T17" s="28">
+        <v>33.890999999999998</v>
+      </c>
+      <c r="U17" s="189">
+        <v>53.915999999999997</v>
+      </c>
+      <c r="V17" s="91">
+        <v>30.864000000000001</v>
+      </c>
+      <c r="W17" s="40">
+        <v>42.018999999999998</v>
+      </c>
+      <c r="X17" s="193">
+        <v>33.103999999999999</v>
+      </c>
+      <c r="Y17" s="234">
+        <v>28.893999999999998</v>
+      </c>
+      <c r="Z17" s="29">
+        <v>28.655999999999999</v>
+      </c>
+      <c r="AA17" s="32">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="AB17" s="24">
+        <v>31.856000000000002</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="216"/>
-      <c r="B18" s="217" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="35" t="s">
+      <c r="A18" s="231"/>
+      <c r="B18" s="235"/>
+      <c r="C18" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="141">
-        <v>44.015000000000001</v>
-      </c>
-      <c r="F18" s="18">
-        <v>46.975000000000001</v>
-      </c>
-      <c r="G18" s="119">
-        <v>40.731999999999999</v>
-      </c>
-      <c r="H18" s="177">
-        <v>36.220999999999997</v>
-      </c>
-      <c r="I18" s="162">
-        <v>44.176000000000002</v>
-      </c>
-      <c r="J18" s="126">
-        <v>41.243000000000002</v>
-      </c>
-      <c r="K18" s="189">
-        <v>33.155999999999999</v>
-      </c>
-      <c r="L18" s="17">
-        <v>33.212000000000003</v>
-      </c>
-      <c r="M18" s="15">
-        <v>57.716000000000001</v>
-      </c>
-      <c r="N18" s="113">
-        <v>37.366</v>
-      </c>
-      <c r="O18" s="218">
-        <v>35.841999999999999</v>
-      </c>
-      <c r="P18" s="109">
-        <v>52.939</v>
-      </c>
-      <c r="Q18" s="85">
-        <v>31.253</v>
-      </c>
-      <c r="R18" s="190">
-        <v>33.040999999999997</v>
-      </c>
-      <c r="S18" s="30">
-        <v>30.943000000000001</v>
-      </c>
-      <c r="T18" s="28">
-        <v>33.890999999999998</v>
-      </c>
-      <c r="U18" s="185">
-        <v>53.915999999999997</v>
-      </c>
-      <c r="V18" s="91">
-        <v>30.864000000000001</v>
-      </c>
-      <c r="W18" s="40">
-        <v>42.018999999999998</v>
-      </c>
-      <c r="X18" s="189">
-        <v>33.103999999999999</v>
-      </c>
-      <c r="Y18" s="219">
-        <v>28.893999999999998</v>
-      </c>
-      <c r="Z18" s="29">
-        <v>28.655999999999999</v>
-      </c>
-      <c r="AA18" s="32">
-        <v>32.533000000000001</v>
-      </c>
-      <c r="AB18" s="24">
-        <v>31.856000000000002</v>
+      <c r="E18" s="236">
+        <v>42.604999999999997</v>
+      </c>
+      <c r="F18" s="237">
+        <v>43.125999999999998</v>
+      </c>
+      <c r="G18" s="74">
+        <v>46.700000000000003</v>
+      </c>
+      <c r="H18" s="48">
+        <v>34.505000000000003</v>
+      </c>
+      <c r="I18" s="238">
+        <v>47.280999999999999</v>
+      </c>
+      <c r="J18" s="82">
+        <v>40.838999999999999</v>
+      </c>
+      <c r="K18" s="239">
+        <v>31.774999999999999</v>
+      </c>
+      <c r="L18" s="240">
+        <v>31.295000000000002</v>
+      </c>
+      <c r="M18" s="236">
+        <v>42.625</v>
+      </c>
+      <c r="N18" s="241">
+        <v>34.332999999999998</v>
+      </c>
+      <c r="O18" s="242">
+        <v>37.286000000000001</v>
+      </c>
+      <c r="P18" s="15">
+        <v>50.643999999999998</v>
+      </c>
+      <c r="Q18" s="242">
+        <v>37.273000000000003</v>
+      </c>
+      <c r="R18" s="59">
+        <v>34.121000000000002</v>
+      </c>
+      <c r="S18" s="193">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="T18" s="102">
+        <v>33.347000000000001</v>
+      </c>
+      <c r="U18" s="158">
+        <v>42.076000000000001</v>
+      </c>
+      <c r="V18" s="13">
+        <v>39.887</v>
+      </c>
+      <c r="W18" s="15">
+        <v>50.643999999999998</v>
+      </c>
+      <c r="X18" s="64">
+        <v>37.667000000000002</v>
+      </c>
+      <c r="Y18" s="29">
+        <v>29.359000000000002</v>
+      </c>
+      <c r="Z18" s="181">
+        <v>34.923999999999999</v>
+      </c>
+      <c r="AA18" s="112">
+        <v>38.362000000000002</v>
+      </c>
+      <c r="AB18" s="243">
+        <v>33.170999999999999</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="216"/>
-      <c r="B19" s="220"/>
-      <c r="C19" s="35" t="s">
+      <c r="A19" s="231"/>
+      <c r="B19" s="244" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="221">
-        <v>42.604999999999997</v>
-      </c>
-      <c r="F19" s="222">
-        <v>43.125999999999998</v>
-      </c>
-      <c r="G19" s="74">
-        <v>46.700000000000003</v>
-      </c>
-      <c r="H19" s="48">
-        <v>34.505000000000003</v>
-      </c>
-      <c r="I19" s="223">
-        <v>47.280999999999999</v>
-      </c>
-      <c r="J19" s="82">
-        <v>40.838999999999999</v>
-      </c>
-      <c r="K19" s="224">
-        <v>31.774999999999999</v>
-      </c>
-      <c r="L19" s="225">
-        <v>31.295000000000002</v>
-      </c>
-      <c r="M19" s="221">
-        <v>42.625</v>
-      </c>
-      <c r="N19" s="226">
-        <v>34.332999999999998</v>
-      </c>
-      <c r="O19" s="227">
-        <v>37.286000000000001</v>
-      </c>
-      <c r="P19" s="15">
-        <v>50.643999999999998</v>
-      </c>
-      <c r="Q19" s="227">
-        <v>37.273000000000003</v>
-      </c>
-      <c r="R19" s="59">
-        <v>34.121000000000002</v>
-      </c>
-      <c r="S19" s="189">
-        <v>32.607999999999997</v>
-      </c>
-      <c r="T19" s="102">
-        <v>33.347000000000001</v>
-      </c>
-      <c r="U19" s="154">
-        <v>42.076000000000001</v>
-      </c>
-      <c r="V19" s="13">
-        <v>39.887</v>
-      </c>
-      <c r="W19" s="15">
-        <v>50.643999999999998</v>
-      </c>
-      <c r="X19" s="64">
-        <v>37.667000000000002</v>
-      </c>
-      <c r="Y19" s="29">
-        <v>29.359000000000002</v>
-      </c>
-      <c r="Z19" s="177">
-        <v>34.923999999999999</v>
-      </c>
-      <c r="AA19" s="110">
-        <v>38.362000000000002</v>
-      </c>
-      <c r="AB19" s="195">
-        <v>33.170999999999999</v>
+      <c r="C19" s="123" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="124" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-0.63</v>
+      </c>
+      <c r="F19" s="190">
+        <v>-0.93999999999999995</v>
+      </c>
+      <c r="G19" s="62">
+        <v>-1.21</v>
+      </c>
+      <c r="H19" s="162">
+        <v>-1</v>
+      </c>
+      <c r="I19" s="245">
+        <v>-1.01</v>
+      </c>
+      <c r="J19" s="188">
+        <v>-0.89000000000000001</v>
+      </c>
+      <c r="K19" s="130">
+        <v>-1.48</v>
+      </c>
+      <c r="L19" s="96">
+        <v>-1.6100000000000001</v>
+      </c>
+      <c r="M19" s="188">
+        <v>-0.89000000000000001</v>
+      </c>
+      <c r="N19" s="238">
+        <v>-0.87</v>
+      </c>
+      <c r="O19" s="57">
+        <v>-1.24</v>
+      </c>
+      <c r="P19" s="128">
+        <v>-0.93000000000000005</v>
+      </c>
+      <c r="Q19" s="168">
+        <v>-1.5900000000000001</v>
+      </c>
+      <c r="R19" s="68">
+        <v>-1.4099999999999999</v>
+      </c>
+      <c r="S19" s="183">
+        <v>-1.6200000000000001</v>
+      </c>
+      <c r="T19" s="29">
+        <v>-2.1299999999999999</v>
+      </c>
+      <c r="U19" s="237">
+        <v>-1.1599999999999999</v>
+      </c>
+      <c r="V19" s="129">
+        <v>-0.81999999999999995</v>
+      </c>
+      <c r="W19" s="62">
+        <v>-1.21</v>
+      </c>
+      <c r="X19" s="19">
+        <v>-1.2</v>
+      </c>
+      <c r="Y19" s="50">
+        <v>-1.6899999999999999</v>
+      </c>
+      <c r="Z19" s="40">
+        <v>-1.4399999999999999</v>
+      </c>
+      <c r="AA19" s="246">
+        <v>-1.0800000000000001</v>
+      </c>
+      <c r="AB19" s="173">
+        <v>-1.6699999999999999</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="216"/>
-      <c r="B20" s="228" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="36" t="s">
+      <c r="A20" s="231"/>
+      <c r="B20" s="244" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="15">
-        <v>-0.63</v>
-      </c>
-      <c r="F20" s="186">
-        <v>-0.93999999999999995</v>
-      </c>
-      <c r="G20" s="62">
-        <v>-1.21</v>
-      </c>
-      <c r="H20" s="158">
-        <v>-1</v>
-      </c>
-      <c r="I20" s="229">
-        <v>-1.01</v>
-      </c>
-      <c r="J20" s="184">
-        <v>-0.89000000000000001</v>
-      </c>
-      <c r="K20" s="126">
-        <v>-1.48</v>
-      </c>
-      <c r="L20" s="96">
-        <v>-1.6100000000000001</v>
-      </c>
-      <c r="M20" s="184">
-        <v>-0.89000000000000001</v>
-      </c>
-      <c r="N20" s="223">
-        <v>-0.87</v>
-      </c>
-      <c r="O20" s="57">
-        <v>-1.24</v>
-      </c>
-      <c r="P20" s="124">
-        <v>-0.93000000000000005</v>
-      </c>
-      <c r="Q20" s="164">
-        <v>-1.5900000000000001</v>
-      </c>
-      <c r="R20" s="68">
-        <v>-1.4099999999999999</v>
-      </c>
-      <c r="S20" s="179">
-        <v>-1.6200000000000001</v>
-      </c>
-      <c r="T20" s="29">
-        <v>-2.1299999999999999</v>
-      </c>
-      <c r="U20" s="222">
-        <v>-1.1599999999999999</v>
-      </c>
-      <c r="V20" s="125">
-        <v>-0.81999999999999995</v>
-      </c>
-      <c r="W20" s="62">
-        <v>-1.21</v>
-      </c>
-      <c r="X20" s="19">
-        <v>-1.2</v>
-      </c>
-      <c r="Y20" s="50">
-        <v>-1.6899999999999999</v>
-      </c>
-      <c r="Z20" s="40">
-        <v>-1.4399999999999999</v>
-      </c>
-      <c r="AA20" s="230">
-        <v>-1.0800000000000001</v>
-      </c>
-      <c r="AB20" s="169">
-        <v>-1.6699999999999999</v>
+      <c r="C20" s="123" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="124" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="247">
+        <v>2.1200000000000001</v>
+      </c>
+      <c r="F20" s="15">
+        <v>2.1000000000000001</v>
+      </c>
+      <c r="G20" s="119">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="H20" s="37">
+        <v>2.1299999999999999</v>
+      </c>
+      <c r="I20" s="159">
+        <v>2.1499999999999999</v>
+      </c>
+      <c r="J20" s="248">
+        <v>2.1600000000000001</v>
+      </c>
+      <c r="K20" s="187">
+        <v>2.1400000000000001</v>
+      </c>
+      <c r="L20" s="72">
+        <v>2.21</v>
+      </c>
+      <c r="M20" s="15">
+        <v>2.1000000000000001</v>
+      </c>
+      <c r="N20" s="247">
+        <v>2.1200000000000001</v>
+      </c>
+      <c r="O20" s="247">
+        <v>2.1200000000000001</v>
+      </c>
+      <c r="P20" s="249">
+        <v>2.1099999999999999</v>
+      </c>
+      <c r="Q20" s="159">
+        <v>2.1499999999999999</v>
+      </c>
+      <c r="R20" s="250">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S20" s="37">
+        <v>2.1299999999999999</v>
+      </c>
+      <c r="T20" s="119">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="U20" s="72">
+        <v>2.21</v>
+      </c>
+      <c r="V20" s="248">
+        <v>2.1600000000000001</v>
+      </c>
+      <c r="W20" s="119">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="X20" s="251">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="Y20" s="251">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="Z20" s="159">
+        <v>2.1499999999999999</v>
+      </c>
+      <c r="AA20" s="29">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="AB20" s="187">
+        <v>2.1400000000000001</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="216"/>
-      <c r="B21" s="228" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="231">
-        <v>2.1200000000000001</v>
+      <c r="A21" s="231"/>
+      <c r="B21" s="232" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="123" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="124" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="68">
+        <v>9.5414972223221</v>
       </c>
       <c r="F21" s="15">
-        <v>2.1000000000000001</v>
-      </c>
-      <c r="G21" s="117">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="H21" s="37">
-        <v>2.1299999999999999</v>
-      </c>
-      <c r="I21" s="155">
-        <v>2.1499999999999999</v>
-      </c>
-      <c r="J21" s="232">
-        <v>2.1600000000000001</v>
-      </c>
-      <c r="K21" s="183">
-        <v>2.1400000000000001</v>
-      </c>
-      <c r="L21" s="72">
-        <v>2.21</v>
-      </c>
-      <c r="M21" s="15">
-        <v>2.1000000000000001</v>
-      </c>
-      <c r="N21" s="231">
-        <v>2.1200000000000001</v>
-      </c>
-      <c r="O21" s="231">
-        <v>2.1200000000000001</v>
-      </c>
-      <c r="P21" s="233">
-        <v>2.1099999999999999</v>
-      </c>
-      <c r="Q21" s="155">
-        <v>2.1499999999999999</v>
-      </c>
-      <c r="R21" s="234">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="S21" s="37">
-        <v>2.1299999999999999</v>
-      </c>
-      <c r="T21" s="117">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="U21" s="72">
-        <v>2.21</v>
-      </c>
-      <c r="V21" s="232">
-        <v>2.1600000000000001</v>
-      </c>
-      <c r="W21" s="117">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="X21" s="235">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="Y21" s="235">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="Z21" s="155">
-        <v>2.1499999999999999</v>
-      </c>
-      <c r="AA21" s="29">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="AB21" s="183">
-        <v>2.1400000000000001</v>
+        <v>8.9621786170560007</v>
+      </c>
+      <c r="G21" s="164">
+        <v>9.0604552871149995</v>
+      </c>
+      <c r="H21" s="146">
+        <v>9.3920249916490004</v>
+      </c>
+      <c r="I21" s="46">
+        <v>9.4529318523390007</v>
+      </c>
+      <c r="J21" s="252">
+        <v>9.4725931996879993</v>
+      </c>
+      <c r="K21" s="236">
+        <v>9.3798937271960003</v>
+      </c>
+      <c r="L21" s="112">
+        <v>9.5981756525529995</v>
+      </c>
+      <c r="M21" s="10">
+        <v>9.0371196393689992</v>
+      </c>
+      <c r="N21" s="154">
+        <v>9.2038149054070004</v>
+      </c>
+      <c r="O21" s="86">
+        <v>9.7555741841170001</v>
+      </c>
+      <c r="P21" s="51">
+        <v>9.6268718150330006</v>
+      </c>
+      <c r="Q21" s="138">
+        <v>9.3676183072330002</v>
+      </c>
+      <c r="R21" s="23">
+        <v>9.6343867462879995</v>
+      </c>
+      <c r="S21" s="104">
+        <v>9.6979779457300008</v>
+      </c>
+      <c r="T21" s="29">
+        <v>10.069228160744</v>
+      </c>
+      <c r="U21" s="31">
+        <v>9.8071255062729996</v>
+      </c>
+      <c r="V21" s="233">
+        <v>9.7942627678769991</v>
+      </c>
+      <c r="W21" s="64">
+        <v>9.6406330734280008</v>
+      </c>
+      <c r="X21" s="253">
+        <v>9.6945998876720001</v>
+      </c>
+      <c r="Y21" s="127">
+        <v>9.7486063536870002</v>
+      </c>
+      <c r="Z21" s="81">
+        <v>9.5257409073930006</v>
+      </c>
+      <c r="AA21" s="17">
+        <v>9.8923115586910004</v>
+      </c>
+      <c r="AB21" s="175">
+        <v>9.4383999222329997</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="216"/>
-      <c r="B22" s="217" t="s">
+      <c r="A22" s="231"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="123" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="124" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="61">
-        <v>9.5</v>
-      </c>
-      <c r="F22" s="15">
-        <v>9</v>
-      </c>
-      <c r="G22" s="236">
-        <v>9.0999999999999996</v>
-      </c>
-      <c r="H22" s="134">
-        <v>9.4000000000000004</v>
+      <c r="E22" s="117">
+        <v>-2.8655555555555559</v>
+      </c>
+      <c r="F22" s="20">
+        <v>-2.5811111111111109</v>
+      </c>
+      <c r="G22" s="254">
+        <v>-3.0544444444444441</v>
+      </c>
+      <c r="H22" s="45">
+        <v>-2.5466666666666669</v>
       </c>
       <c r="I22" s="61">
-        <v>9.5</v>
-      </c>
-      <c r="J22" s="61">
-        <v>9.5</v>
-      </c>
-      <c r="K22" s="134">
-        <v>9.4000000000000004</v>
-      </c>
-      <c r="L22" s="153">
-        <v>9.5999999999999996</v>
-      </c>
-      <c r="M22" s="15">
-        <v>9</v>
+        <v>-2.5388888888888892</v>
+      </c>
+      <c r="J22" s="56">
+        <v>-3.3700000000000001</v>
+      </c>
+      <c r="K22" s="56">
+        <v>-3.367777777777778</v>
+      </c>
+      <c r="L22" s="79">
+        <v>-2.4233333333333338</v>
+      </c>
+      <c r="M22" s="126">
+        <v>-2.6200000000000001</v>
       </c>
       <c r="N22" s="138">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="O22" s="26">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="P22" s="153">
-        <v>9.5999999999999996</v>
-      </c>
-      <c r="Q22" s="134">
-        <v>9.4000000000000004</v>
-      </c>
-      <c r="R22" s="153">
-        <v>9.5999999999999996</v>
-      </c>
-      <c r="S22" s="65">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="T22" s="29">
-        <v>10.1</v>
-      </c>
-      <c r="U22" s="26">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="V22" s="26">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="W22" s="153">
-        <v>9.5999999999999996</v>
-      </c>
-      <c r="X22" s="65">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="Y22" s="65">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="Z22" s="61">
-        <v>9.5</v>
-      </c>
-      <c r="AA22" s="28">
-        <v>9.9000000000000004</v>
-      </c>
-      <c r="AB22" s="134">
-        <v>9.4000000000000004</v>
+        <v>-2.776666666666666</v>
+      </c>
+      <c r="O22" s="137">
+        <v>-2.6388888888888888</v>
+      </c>
+      <c r="P22" s="246">
+        <v>-2.953333333333334</v>
+      </c>
+      <c r="Q22" s="255">
+        <v>-2.6566666666666658</v>
+      </c>
+      <c r="R22" s="69">
+        <v>-2.177777777777778</v>
+      </c>
+      <c r="S22" s="29">
+        <v>-1.108888888888889</v>
+      </c>
+      <c r="T22" s="88">
+        <v>-2.1055555555555561</v>
+      </c>
+      <c r="U22" s="145">
+        <v>-2.4988888888888892</v>
+      </c>
+      <c r="V22" s="191">
+        <v>-2.1899999999999999</v>
+      </c>
+      <c r="W22" s="134">
+        <v>-2.3599999999999999</v>
+      </c>
+      <c r="X22" s="43">
+        <v>-2.4533333333333331</v>
+      </c>
+      <c r="Y22" s="187">
+        <v>-2.98</v>
+      </c>
+      <c r="Z22" s="51">
+        <v>-2.1600000000000001</v>
+      </c>
+      <c r="AA22" s="256">
+        <v>-3.108888888888889</v>
+      </c>
+      <c r="AB22" s="15">
+        <v>-3.7344444444444438</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="216"/>
-      <c r="B23" s="220"/>
-      <c r="C23" s="35" t="s">
+      <c r="A23" s="231"/>
+      <c r="B23" s="235"/>
+      <c r="C23" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="124" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="115">
-        <v>-2.8655555555555559</v>
-      </c>
-      <c r="F23" s="20">
-        <v>-2.5811111111111109</v>
-      </c>
-      <c r="G23" s="237">
-        <v>-3.0544444444444441</v>
-      </c>
-      <c r="H23" s="45">
-        <v>-2.5466666666666669</v>
-      </c>
-      <c r="I23" s="61">
-        <v>-2.5388888888888892</v>
-      </c>
-      <c r="J23" s="56">
-        <v>-3.3700000000000001</v>
-      </c>
-      <c r="K23" s="56">
-        <v>-3.367777777777778</v>
-      </c>
-      <c r="L23" s="79">
-        <v>-2.4233333333333338</v>
-      </c>
-      <c r="M23" s="122">
-        <v>-2.6200000000000001</v>
-      </c>
-      <c r="N23" s="134">
-        <v>-2.776666666666666</v>
-      </c>
-      <c r="O23" s="133">
-        <v>-2.6388888888888888</v>
-      </c>
-      <c r="P23" s="230">
-        <v>-2.953333333333334</v>
-      </c>
-      <c r="Q23" s="238">
-        <v>-2.6566666666666658</v>
-      </c>
-      <c r="R23" s="69">
-        <v>-2.177777777777778</v>
-      </c>
-      <c r="S23" s="29">
-        <v>-1.108888888888889</v>
-      </c>
-      <c r="T23" s="88">
-        <v>-2.1055555555555561</v>
-      </c>
-      <c r="U23" s="141">
-        <v>-2.4988888888888892</v>
-      </c>
-      <c r="V23" s="187">
-        <v>-2.1899999999999999</v>
-      </c>
-      <c r="W23" s="130">
-        <v>-2.3599999999999999</v>
-      </c>
-      <c r="X23" s="43">
-        <v>-2.4533333333333331</v>
-      </c>
-      <c r="Y23" s="183">
-        <v>-2.98</v>
-      </c>
-      <c r="Z23" s="51">
-        <v>-2.1600000000000001</v>
-      </c>
-      <c r="AA23" s="191">
-        <v>-3.108888888888889</v>
-      </c>
-      <c r="AB23" s="15">
-        <v>-3.7344444444444438</v>
+      <c r="E23" s="257"/>
+      <c r="F23" s="257"/>
+      <c r="G23" s="257"/>
+      <c r="H23" s="133">
+        <v>7.4800000000000004</v>
+      </c>
+      <c r="I23" s="96">
+        <v>7.4299999999999997</v>
+      </c>
+      <c r="J23" s="17">
+        <v>7.9000000000000004</v>
+      </c>
+      <c r="K23" s="180">
+        <v>7.6200000000000001</v>
+      </c>
+      <c r="L23" s="253">
+        <v>7.4500000000000002</v>
+      </c>
+      <c r="M23" s="12">
+        <v>7.5899999999999999</v>
+      </c>
+      <c r="N23" s="242">
+        <v>7.3600000000000003</v>
+      </c>
+      <c r="O23" s="258">
+        <v>7.5999999999999996</v>
+      </c>
+      <c r="P23" s="127">
+        <v>7.5599999999999996</v>
+      </c>
+      <c r="Q23" s="259">
+        <v>7.3499999999999996</v>
+      </c>
+      <c r="R23" s="181">
+        <v>7.6399999999999997</v>
+      </c>
+      <c r="S23" s="16">
+        <v>7.2800000000000002</v>
+      </c>
+      <c r="T23" s="29">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="U23" s="43">
+        <v>7</v>
+      </c>
+      <c r="V23" s="61">
+        <v>6.9199999999999999</v>
+      </c>
+      <c r="W23" s="19">
+        <v>6.7300000000000004</v>
+      </c>
+      <c r="X23" s="150">
+        <v>7.79</v>
+      </c>
+      <c r="Y23" s="15">
+        <v>5.7699999999999996</v>
+      </c>
+      <c r="Z23" s="56">
+        <v>6.1200000000000001</v>
+      </c>
+      <c r="AA23" s="79">
+        <v>7.0300000000000002</v>
+      </c>
+      <c r="AB23" s="14">
+        <v>6.46</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="216"/>
-      <c r="B24" s="228" t="s">
+      <c r="A24" s="231"/>
+      <c r="B24" s="244" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="239">
+      <c r="E24" s="260">
         <v>2.0899999999999999</v>
       </c>
       <c r="F24" s="42">
         <v>1.3500000000000001</v>
       </c>
-      <c r="G24" s="203">
+      <c r="G24" s="261">
         <v>4.0700000000000003</v>
       </c>
-      <c r="H24" s="240">
+      <c r="H24" s="262">
         <v>0.44</v>
       </c>
-      <c r="I24" s="241">
+      <c r="I24" s="263">
         <v>3.21</v>
       </c>
       <c r="J24" s="15">
@@ -4609,13 +5187,13 @@
       <c r="K24" s="13">
         <v>13.44</v>
       </c>
-      <c r="L24" s="205">
+      <c r="L24" s="264">
         <v>7.8899999999999997</v>
       </c>
       <c r="M24" s="42">
         <v>1.3300000000000001</v>
       </c>
-      <c r="N24" s="116">
+      <c r="N24" s="118">
         <v>2.1899999999999999</v>
       </c>
       <c r="O24" s="64">
@@ -4624,16 +5202,16 @@
       <c r="P24" s="74">
         <v>4.8899999999999997</v>
       </c>
-      <c r="Q24" s="204">
+      <c r="Q24" s="265">
         <v>6.0199999999999996</v>
       </c>
       <c r="R24" s="53">
         <v>23.41</v>
       </c>
-      <c r="S24" s="129">
+      <c r="S24" s="133">
         <v>18.010000000000002</v>
       </c>
-      <c r="T24" s="135">
+      <c r="T24" s="139">
         <v>3.8900000000000001</v>
       </c>
       <c r="U24" s="67">
@@ -4648,34 +5226,34 @@
       <c r="X24" s="58">
         <v>6.0899999999999999</v>
       </c>
-      <c r="Y24" s="242">
+      <c r="Y24" s="266">
         <v>9.1600000000000001</v>
       </c>
-      <c r="Z24" s="243"/>
-      <c r="AA24" s="243"/>
-      <c r="AB24" s="243"/>
+      <c r="Z24" s="257"/>
+      <c r="AA24" s="257"/>
+      <c r="AB24" s="257"/>
     </row>
     <row r="25">
-      <c r="A25" s="216"/>
-      <c r="B25" s="228" t="s">
+      <c r="A25" s="231"/>
+      <c r="B25" s="244" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="35" t="s">
+      <c r="C25" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="124" t="s">
         <v>72</v>
       </c>
       <c r="E25" s="56">
         <v>8</v>
       </c>
-      <c r="F25" s="244">
+      <c r="F25" s="267">
         <v>9.4786699999999993</v>
       </c>
       <c r="G25" s="63">
         <v>15.934100000000001</v>
       </c>
-      <c r="H25" s="245">
+      <c r="H25" s="268">
         <v>7.8947399999999996</v>
       </c>
       <c r="I25" s="37">
@@ -4684,7 +5262,7 @@
       <c r="J25" s="15">
         <v>1.88679</v>
       </c>
-      <c r="K25" s="203">
+      <c r="K25" s="261">
         <v>8.6956500000000005</v>
       </c>
       <c r="L25" s="83">
@@ -4693,10 +5271,10 @@
       <c r="M25" s="75">
         <v>10.216100000000001</v>
       </c>
-      <c r="N25" s="191">
+      <c r="N25" s="256">
         <v>12.442399999999999</v>
       </c>
-      <c r="O25" s="137">
+      <c r="O25" s="141">
         <v>9.1324199999999998</v>
       </c>
       <c r="P25" s="42">
@@ -4705,16 +5283,16 @@
       <c r="Q25" s="38">
         <v>12.6866</v>
       </c>
-      <c r="R25" s="122">
+      <c r="R25" s="126">
         <v>20.7547</v>
       </c>
-      <c r="S25" s="194">
+      <c r="S25" s="269">
         <v>15.315300000000001</v>
       </c>
       <c r="T25" s="65">
         <v>30.1205</v>
       </c>
-      <c r="U25" s="229">
+      <c r="U25" s="245">
         <v>13.084099999999999</v>
       </c>
       <c r="V25" s="39">
@@ -4726,37 +5304,37 @@
       <c r="X25" s="103">
         <v>36.604799999999997</v>
       </c>
-      <c r="Y25" s="151">
+      <c r="Y25" s="155">
         <v>14.8276</v>
       </c>
-      <c r="Z25" s="243"/>
-      <c r="AA25" s="243"/>
-      <c r="AB25" s="243"/>
+      <c r="Z25" s="257"/>
+      <c r="AA25" s="257"/>
+      <c r="AB25" s="257"/>
     </row>
     <row r="26">
-      <c r="A26" s="216"/>
-      <c r="B26" s="228" t="s">
+      <c r="A26" s="231"/>
+      <c r="B26" s="244" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="36" t="s">
+      <c r="C26" s="123" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="124" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="246">
+      <c r="E26" s="270">
         <v>2.3900000000000001</v>
       </c>
-      <c r="F26" s="167">
+      <c r="F26" s="171">
         <v>1.79</v>
       </c>
-      <c r="G26" s="207">
+      <c r="G26" s="271">
         <v>2.75</v>
       </c>
       <c r="H26" s="78">
         <v>1.99</v>
       </c>
-      <c r="I26" s="247">
+      <c r="I26" s="272">
         <v>2.3599999999999999</v>
       </c>
       <c r="J26" s="15">
@@ -4768,22 +5346,22 @@
       <c r="L26" s="63">
         <v>6.8399999999999999</v>
       </c>
-      <c r="M26" s="248">
+      <c r="M26" s="273">
         <v>2.46</v>
       </c>
-      <c r="N26" s="242">
+      <c r="N26" s="266">
         <v>7.29</v>
       </c>
-      <c r="O26" s="239">
+      <c r="O26" s="260">
         <v>2.7599999999999998</v>
       </c>
-      <c r="P26" s="249">
+      <c r="P26" s="274">
         <v>5.1699999999999999</v>
       </c>
-      <c r="Q26" s="250">
+      <c r="Q26" s="275">
         <v>4.9800000000000004</v>
       </c>
-      <c r="R26" s="251">
+      <c r="R26" s="276">
         <v>6.0700000000000003</v>
       </c>
       <c r="S26" s="29">
@@ -4798,13 +5376,13 @@
       <c r="V26" s="10">
         <v>2.6099999999999999</v>
       </c>
-      <c r="W26" s="224">
+      <c r="W26" s="239">
         <v>16.359999999999999</v>
       </c>
-      <c r="X26" s="150">
+      <c r="X26" s="154">
         <v>5.1200000000000001</v>
       </c>
-      <c r="Y26" s="252">
+      <c r="Y26" s="277">
         <v>9.5199999999999996</v>
       </c>
       <c r="Z26" s="61">
@@ -4813,31 +5391,31 @@
       <c r="AA26" s="14">
         <v>6.0099999999999998</v>
       </c>
-      <c r="AB26" s="137">
+      <c r="AB26" s="141">
         <v>4.1699999999999999</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="216"/>
-      <c r="B27" s="228" t="s">
+      <c r="A27" s="231"/>
+      <c r="B27" s="244" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="123" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="124" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="253">
+      <c r="E27" s="278">
         <v>17.539999999999999</v>
       </c>
-      <c r="F27" s="149">
+      <c r="F27" s="153">
         <v>10.289999999999999</v>
       </c>
       <c r="G27" s="29">
         <v>34.880000000000003</v>
       </c>
-      <c r="H27" s="205">
+      <c r="H27" s="264">
         <v>11.48</v>
       </c>
       <c r="I27" s="58">
@@ -4846,13 +5424,13 @@
       <c r="J27" s="38">
         <v>9.8000000000000007</v>
       </c>
-      <c r="K27" s="135">
+      <c r="K27" s="139">
         <v>6.6699999999999999</v>
       </c>
-      <c r="L27" s="133">
+      <c r="L27" s="137">
         <v>15.57</v>
       </c>
-      <c r="M27" s="248">
+      <c r="M27" s="273">
         <v>3.77</v>
       </c>
       <c r="N27" s="60">
@@ -4861,34 +5439,34 @@
       <c r="O27" s="99">
         <v>4.9500000000000002</v>
       </c>
-      <c r="P27" s="203">
+      <c r="P27" s="261">
         <v>6.9500000000000002</v>
       </c>
       <c r="Q27" s="43">
         <v>17.920000000000002</v>
       </c>
-      <c r="R27" s="254">
+      <c r="R27" s="279">
         <v>12.5</v>
       </c>
-      <c r="S27" s="255">
+      <c r="S27" s="252">
         <v>17.129999999999999</v>
       </c>
       <c r="T27" s="51">
         <v>21.649999999999999</v>
       </c>
-      <c r="U27" s="118">
+      <c r="U27" s="120">
         <v>23.23</v>
       </c>
-      <c r="V27" s="213">
+      <c r="V27" s="226">
         <v>15.08</v>
       </c>
-      <c r="W27" s="237">
+      <c r="W27" s="254">
         <v>10.359999999999999</v>
       </c>
       <c r="X27" s="20">
         <v>16.289999999999999</v>
       </c>
-      <c r="Y27" s="115">
+      <c r="Y27" s="117">
         <v>12.69</v>
       </c>
       <c r="Z27" s="19">
@@ -4902,50 +5480,50 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="216"/>
-      <c r="B28" s="228" t="s">
+      <c r="A28" s="231"/>
+      <c r="B28" s="244" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="123" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="124" t="s">
         <v>80</v>
       </c>
       <c r="E28" s="15">
         <v>0.20999999999999999</v>
       </c>
-      <c r="F28" s="186">
+      <c r="F28" s="190">
         <v>0.27000000000000002</v>
       </c>
-      <c r="G28" s="251">
+      <c r="G28" s="276">
         <v>0.28999999999999998</v>
       </c>
       <c r="H28" s="19">
         <v>0.32000000000000001</v>
       </c>
-      <c r="I28" s="256">
+      <c r="I28" s="280">
         <v>0.35999999999999999</v>
       </c>
-      <c r="J28" s="257">
+      <c r="J28" s="281">
         <v>0.34999999999999998</v>
       </c>
       <c r="K28" s="48">
         <v>0.42999999999999999</v>
       </c>
-      <c r="L28" s="187">
+      <c r="L28" s="191">
         <v>0.38</v>
       </c>
-      <c r="M28" s="257">
+      <c r="M28" s="281">
         <v>0.34999999999999998</v>
       </c>
-      <c r="N28" s="256">
+      <c r="N28" s="280">
         <v>0.35999999999999999</v>
       </c>
-      <c r="O28" s="128">
+      <c r="O28" s="132">
         <v>0.40999999999999998</v>
       </c>
-      <c r="P28" s="187">
+      <c r="P28" s="191">
         <v>0.38</v>
       </c>
       <c r="Q28" s="96">
@@ -4954,19 +5532,19 @@
       <c r="R28" s="71">
         <v>0.45000000000000001</v>
       </c>
-      <c r="S28" s="168">
+      <c r="S28" s="172">
         <v>0.44</v>
       </c>
       <c r="T28" s="29">
         <v>0.5</v>
       </c>
-      <c r="U28" s="128">
+      <c r="U28" s="132">
         <v>0.40999999999999998</v>
       </c>
       <c r="V28" s="49">
         <v>0.46999999999999997</v>
       </c>
-      <c r="W28" s="206">
+      <c r="W28" s="282">
         <v>0.29999999999999999</v>
       </c>
       <c r="X28" s="48">
@@ -4975,10 +5553,10 @@
       <c r="Y28" s="71">
         <v>0.45000000000000001</v>
       </c>
-      <c r="Z28" s="128">
+      <c r="Z28" s="132">
         <v>0.40999999999999998</v>
       </c>
-      <c r="AA28" s="128">
+      <c r="AA28" s="132">
         <v>0.40999999999999998</v>
       </c>
       <c r="AB28" s="10">
@@ -4986,74 +5564,74 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="216"/>
-      <c r="B29" s="228" t="s">
+      <c r="A29" s="231"/>
+      <c r="B29" s="244" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="123" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="E29" s="248">
+      <c r="E29" s="273">
         <v>2</v>
       </c>
       <c r="F29" s="15">
         <v>1.8</v>
       </c>
-      <c r="G29" s="186">
+      <c r="G29" s="190">
         <v>2.5</v>
       </c>
-      <c r="H29" s="193">
+      <c r="H29" s="283">
         <v>2.7000000000000002</v>
       </c>
-      <c r="I29" s="238">
+      <c r="I29" s="255">
         <v>3.2000000000000002</v>
       </c>
-      <c r="J29" s="186">
+      <c r="J29" s="190">
         <v>2.5</v>
       </c>
       <c r="K29" s="29">
         <v>5.2000000000000002</v>
       </c>
-      <c r="L29" s="238">
+      <c r="L29" s="255">
         <v>3.2000000000000002</v>
       </c>
-      <c r="M29" s="222">
+      <c r="M29" s="237">
         <v>3</v>
       </c>
       <c r="N29" s="20">
         <v>3.2999999999999998</v>
       </c>
-      <c r="O29" s="222">
+      <c r="O29" s="237">
         <v>3</v>
       </c>
-      <c r="P29" s="222">
+      <c r="P29" s="237">
         <v>3</v>
       </c>
-      <c r="Q29" s="141">
+      <c r="Q29" s="145">
         <v>3.3999999999999999</v>
       </c>
       <c r="R29" s="19">
         <v>3.1000000000000001</v>
       </c>
-      <c r="S29" s="258">
+      <c r="S29" s="284">
         <v>2.3999999999999999</v>
       </c>
-      <c r="T29" s="205">
+      <c r="T29" s="264">
         <v>2.7999999999999998</v>
       </c>
-      <c r="U29" s="222">
+      <c r="U29" s="237">
         <v>3</v>
       </c>
       <c r="V29" s="19">
         <v>3.1000000000000001</v>
       </c>
-      <c r="W29" s="205">
+      <c r="W29" s="264">
         <v>2.7999999999999998</v>
       </c>
-      <c r="X29" s="193">
+      <c r="X29" s="283">
         <v>2.7000000000000002</v>
       </c>
       <c r="Y29" s="19">
@@ -5065,96 +5643,96 @@
       <c r="AA29" s="50">
         <v>4.2000000000000002</v>
       </c>
-      <c r="AB29" s="222">
+      <c r="AB29" s="237">
         <v>3</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="259"/>
-      <c r="B30" s="260" t="s">
+      <c r="A30" s="285"/>
+      <c r="B30" s="286" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="93" t="s">
+      <c r="C30" s="197" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="94" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="230">
-        <v>-1.7147984280919271</v>
-      </c>
-      <c r="F30" s="237">
-        <v>-1.83258146374831</v>
-      </c>
-      <c r="G30" s="242">
-        <v>-1.5606477482646679</v>
-      </c>
-      <c r="H30" s="121">
-        <v>-1.6607312068216511</v>
-      </c>
-      <c r="I30" s="150">
-        <v>-1.966112856372833</v>
-      </c>
-      <c r="J30" s="244">
-        <v>-2.120263536200091</v>
-      </c>
-      <c r="K30" s="237">
-        <v>-1.83258146374831</v>
+      <c r="D30" s="198" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="125">
+        <v>-1.713238723323588</v>
+      </c>
+      <c r="F30" s="187">
+        <v>-1.8023777645683789</v>
+      </c>
+      <c r="G30" s="237">
+        <v>-1.5841184648543249</v>
+      </c>
+      <c r="H30" s="279">
+        <v>-1.6837132733589411</v>
+      </c>
+      <c r="I30" s="256">
+        <v>-1.968211064060625</v>
+      </c>
+      <c r="J30" s="75">
+        <v>-2.119585499147342</v>
+      </c>
+      <c r="K30" s="165">
+        <v>-1.8096269804140059</v>
       </c>
       <c r="L30" s="29">
-        <v>0.51282362642866375</v>
+        <v>0.5099109031599478</v>
       </c>
       <c r="M30" s="15">
-        <v>-2.6592600369327779</v>
-      </c>
-      <c r="N30" s="239">
-        <v>-2.4079456086518718</v>
-      </c>
-      <c r="O30" s="239">
-        <v>-2.4079456086518718</v>
-      </c>
-      <c r="P30" s="15">
-        <v>-2.6592600369327779</v>
-      </c>
-      <c r="Q30" s="244">
-        <v>-2.120263536200091</v>
-      </c>
-      <c r="R30" s="244">
-        <v>-2.120263536200091</v>
-      </c>
-      <c r="S30" s="239">
-        <v>-2.4079456086518718</v>
-      </c>
-      <c r="T30" s="11">
-        <v>-2.302585092994045</v>
-      </c>
-      <c r="U30" s="163">
-        <v>-2.5257286443082561</v>
-      </c>
-      <c r="V30" s="239">
-        <v>-2.4079456086518718</v>
-      </c>
-      <c r="W30" s="175">
-        <v>-2.0402208285265551</v>
-      </c>
-      <c r="X30" s="261">
-        <v>-1.8971199848858811</v>
-      </c>
-      <c r="Y30" s="13">
-        <v>-1.0498221244986781</v>
-      </c>
-      <c r="Z30" s="243"/>
-      <c r="AA30" s="243"/>
-      <c r="AB30" s="243"/>
+        <v>-2.7294048866793208</v>
+      </c>
+      <c r="N30" s="118">
+        <v>-2.4633720608659422</v>
+      </c>
+      <c r="O30" s="164">
+        <v>-2.447985195777195</v>
+      </c>
+      <c r="P30" s="167">
+        <v>-2.6005206457026242</v>
+      </c>
+      <c r="Q30" s="74">
+        <v>-2.1328438461255019</v>
+      </c>
+      <c r="R30" s="284">
+        <v>-2.1478829848234029</v>
+      </c>
+      <c r="S30" s="287">
+        <v>-2.42794795303453</v>
+      </c>
+      <c r="T30" s="129">
+        <v>-2.3153170991677259</v>
+      </c>
+      <c r="U30" s="272">
+        <v>-2.5568468807089979</v>
+      </c>
+      <c r="V30" s="164">
+        <v>-2.444954794235914</v>
+      </c>
+      <c r="W30" s="128">
+        <v>-2.0754235599151638</v>
+      </c>
+      <c r="X30" s="177">
+        <v>-1.865495994506744</v>
+      </c>
+      <c r="Y30" s="280">
+        <v>-1.0550162885962</v>
+      </c>
+      <c r="Z30" s="257"/>
+      <c r="AA30" s="257"/>
+      <c r="AB30" s="257"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A2:A15"/>
     <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B7:B15"/>
-    <mergeCell ref="A17:A30"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B7:B14"/>
+    <mergeCell ref="A16:A30"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B21:B23"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
